--- a/Result/profitability/6609.xlsx
+++ b/Result/profitability/6609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.72</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08249999999999998</v>
+        <v>-0.06250000000000003</v>
       </c>
       <c r="N2" t="n">
-        <v>14.8425</v>
+        <v>14.2</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.63</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01875000000000002</v>
+        <v>-0.007500000000000021</v>
       </c>
       <c r="N3" t="n">
-        <v>13.7525</v>
+        <v>13.8825</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.54</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02499999999999999</v>
+        <v>0.02874999999999998</v>
       </c>
       <c r="N4" t="n">
-        <v>13.09625</v>
+        <v>13.415</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02874999999999999</v>
+        <v>0.1875</v>
       </c>
       <c r="N5" t="n">
-        <v>13.00375</v>
+        <v>13.4575</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.43</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09875</v>
+        <v>0.12625</v>
       </c>
       <c r="N6" t="n">
-        <v>11.9125</v>
+        <v>13.04125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.91</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.02250000000000002</v>
+        <v>0.11875</v>
       </c>
       <c r="N7" t="n">
-        <v>10.48625</v>
+        <v>13.175</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.84</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02125</v>
+        <v>0.03374999999999996</v>
       </c>
       <c r="N8" t="n">
-        <v>10.7925</v>
+        <v>11.4225</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.14</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.01875000000000001</v>
+        <v>-0.01875000000000003</v>
       </c>
       <c r="N9" t="n">
         <v>10.635</v>
@@ -1645,7 +1645,7 @@
         <v>0.21</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0825</v>
+        <v>-0.08250000000000003</v>
       </c>
       <c r="N10" t="n">
         <v>10.26125</v>
@@ -1772,7 +1772,7 @@
         <v>0.91</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0475</v>
+        <v>-0.04750000000000003</v>
       </c>
       <c r="N11" t="n">
         <v>10.4775</v>
@@ -1899,7 +1899,7 @@
         <v>0.88</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.005000000000000004</v>
+        <v>-0.005000000000000032</v>
       </c>
       <c r="N12" t="n">
         <v>10.95125</v>
@@ -2026,7 +2026,7 @@
         <v>0.22</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.01250000000000001</v>
+        <v>-0.01250000000000004</v>
       </c>
       <c r="N13" t="n">
         <v>10.485</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6609</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>663</v>
+      </c>
+      <c r="D75" t="n">
+        <v>532</v>
+      </c>
+      <c r="E75" t="n">
+        <v>131</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G75" t="n">
+        <v>30</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.54%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>33</v>
+      </c>
+      <c r="K75" t="n">
+        <v>20</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.02749999999999998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.0925</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.4400000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.040000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3414634146341464</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.282828282828283</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.629999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2244897959183672</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
